--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -5934,10 +5934,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119650185</v>
+        <v>119650180</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5946,38 +5946,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515338</v>
+        <v>515044</v>
       </c>
       <c r="R46" t="n">
-        <v>6704861</v>
+        <v>6704840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6014,7 +6017,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>7 fk. +gamla</t>
+          <t>Små tunn fot.??</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6023,6 +6026,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6041,10 +6045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119650180</v>
+        <v>119650185</v>
       </c>
       <c r="B47" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6053,41 +6057,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515044</v>
+        <v>515338</v>
       </c>
       <c r="R47" t="n">
-        <v>6704840</v>
+        <v>6704861</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6124,7 +6125,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Små tunn fot.??</t>
+          <t>7 fk. +gamla</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6133,7 +6134,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6365,10 +6365,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119650182</v>
+        <v>119650186</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6377,25 +6377,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515134</v>
+        <v>515367</v>
       </c>
       <c r="R50" t="n">
-        <v>6704882</v>
+        <v>6704895</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Sammanvuxna till två större fk.</t>
+          <t>3 fk + gamla fk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6472,10 +6472,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119650186</v>
+        <v>119650182</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6484,25 +6484,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6512,10 +6512,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515367</v>
+        <v>515134</v>
       </c>
       <c r="R51" t="n">
-        <v>6704895</v>
+        <v>6704882</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 fk + gamla fk.</t>
+          <t>Sammanvuxna till två större fk.</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -5934,10 +5934,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119650180</v>
+        <v>119650185</v>
       </c>
       <c r="B46" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5946,41 +5946,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515044</v>
+        <v>515338</v>
       </c>
       <c r="R46" t="n">
-        <v>6704840</v>
+        <v>6704861</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6017,7 +6014,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Små tunn fot.??</t>
+          <t>7 fk. +gamla</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6026,7 +6023,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6041,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119650185</v>
+        <v>119650180</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6057,38 +6053,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515338</v>
+        <v>515044</v>
       </c>
       <c r="R47" t="n">
-        <v>6704861</v>
+        <v>6704840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6125,7 +6124,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>7 fk. +gamla</t>
+          <t>Små tunn fot.??</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6134,6 +6133,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6041,10 +6041,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119650180</v>
+        <v>119650188</v>
       </c>
       <c r="B47" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6053,41 +6053,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515044</v>
+        <v>515039</v>
       </c>
       <c r="R47" t="n">
-        <v>6704840</v>
+        <v>6704836</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6124,7 +6121,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Små tunn fot.??</t>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6133,7 +6130,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6254,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119650187</v>
+        <v>119650180</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,25 +6262,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6297,10 +6293,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515163</v>
+        <v>515044</v>
       </c>
       <c r="R49" t="n">
-        <v>6704951</v>
+        <v>6704840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6337,7 +6333,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>5 ex.</t>
+          <t>Små tunn fot.??</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6365,10 +6361,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119650186</v>
+        <v>119647895</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6377,41 +6373,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515367</v>
+        <v>515364</v>
       </c>
       <c r="R50" t="n">
-        <v>6704895</v>
+        <v>6704871</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6438,14 +6443,24 @@
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3 fk + gamla fk.</t>
+          <t>Ett 15-tal fk minst.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6472,7 +6487,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119650182</v>
+        <v>119650181</v>
       </c>
       <c r="B51" t="n">
         <v>91884</v>
@@ -6512,10 +6527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515134</v>
+        <v>515159</v>
       </c>
       <c r="R51" t="n">
-        <v>6704882</v>
+        <v>6704968</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6548,11 +6563,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Sammanvuxna till två större fk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6579,10 +6589,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119650188</v>
+        <v>119650182</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6591,25 +6601,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6619,10 +6629,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515039</v>
+        <v>515134</v>
       </c>
       <c r="R52" t="n">
-        <v>6704836</v>
+        <v>6704882</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6659,7 +6669,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>5 ex.</t>
+          <t>Sammanvuxna till två större fk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6686,10 +6696,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119647895</v>
+        <v>119650187</v>
       </c>
       <c r="B53" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6698,50 +6708,44 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515364</v>
+        <v>515163</v>
       </c>
       <c r="R53" t="n">
-        <v>6704871</v>
+        <v>6704951</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6768,24 +6772,14 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ett 15-tal fk minst.</t>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6794,6 +6788,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6812,10 +6807,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119650181</v>
+        <v>119650186</v>
       </c>
       <c r="B54" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6824,25 +6819,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515159</v>
+        <v>515367</v>
       </c>
       <c r="R54" t="n">
-        <v>6704968</v>
+        <v>6704895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6888,6 +6883,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>3 fk + gamla fk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -5934,10 +5934,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119650185</v>
+        <v>119650180</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5946,38 +5946,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515338</v>
+        <v>515044</v>
       </c>
       <c r="R46" t="n">
-        <v>6704861</v>
+        <v>6704840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6014,7 +6017,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>7 fk. +gamla</t>
+          <t>Små tunn fot.??</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6023,6 +6026,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6041,10 +6045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119650188</v>
+        <v>119650181</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6053,25 +6057,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6081,10 +6085,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515039</v>
+        <v>515159</v>
       </c>
       <c r="R47" t="n">
-        <v>6704836</v>
+        <v>6704968</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6117,11 +6121,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6148,7 +6147,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119650184</v>
+        <v>119650185</v>
       </c>
       <c r="B48" t="n">
         <v>91840</v>
@@ -6188,10 +6187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515345</v>
+        <v>515338</v>
       </c>
       <c r="R48" t="n">
-        <v>6704830</v>
+        <v>6704861</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6224,6 +6223,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>7 fk. +gamla</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6250,10 +6254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119650180</v>
+        <v>119650187</v>
       </c>
       <c r="B49" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6262,25 +6266,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6293,10 +6297,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515044</v>
+        <v>515163</v>
       </c>
       <c r="R49" t="n">
-        <v>6704840</v>
+        <v>6704951</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6333,7 +6337,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Små tunn fot.??</t>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6361,7 +6365,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119647895</v>
+        <v>119650182</v>
       </c>
       <c r="B50" t="n">
         <v>91884</v>
@@ -6394,29 +6398,20 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515364</v>
+        <v>515134</v>
       </c>
       <c r="R50" t="n">
-        <v>6704871</v>
+        <v>6704882</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6443,24 +6438,14 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ett 15-tal fk minst.</t>
+          <t>Sammanvuxna till två större fk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6487,10 +6472,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119650181</v>
+        <v>119650188</v>
       </c>
       <c r="B51" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6499,25 +6484,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6527,10 +6512,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515159</v>
+        <v>515039</v>
       </c>
       <c r="R51" t="n">
-        <v>6704968</v>
+        <v>6704836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6563,6 +6548,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6589,7 +6579,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119650182</v>
+        <v>119647895</v>
       </c>
       <c r="B52" t="n">
         <v>91884</v>
@@ -6622,20 +6612,29 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515134</v>
+        <v>515364</v>
       </c>
       <c r="R52" t="n">
-        <v>6704882</v>
+        <v>6704871</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6662,14 +6661,24 @@
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Sammanvuxna till två större fk.</t>
+          <t>Ett 15-tal fk minst.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6696,7 +6705,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119650187</v>
+        <v>119650186</v>
       </c>
       <c r="B53" t="n">
         <v>91840</v>
@@ -6730,19 +6739,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515163</v>
+        <v>515367</v>
       </c>
       <c r="R53" t="n">
-        <v>6704951</v>
+        <v>6704895</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6779,7 +6785,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>5 ex.</t>
+          <t>3 fk + gamla fk.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6788,7 +6794,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6807,7 +6812,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119650186</v>
+        <v>119650184</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515367</v>
+        <v>515345</v>
       </c>
       <c r="R54" t="n">
-        <v>6704895</v>
+        <v>6704830</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6883,11 +6888,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>3 fk + gamla fk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -5934,10 +5934,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119650180</v>
+        <v>119650186</v>
       </c>
       <c r="B46" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5946,41 +5946,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515044</v>
+        <v>515367</v>
       </c>
       <c r="R46" t="n">
-        <v>6704840</v>
+        <v>6704895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6017,7 +6014,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Små tunn fot.??</t>
+          <t>3 fk + gamla fk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6026,7 +6023,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6041,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119650181</v>
+        <v>119650188</v>
       </c>
       <c r="B47" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6057,25 +6053,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6085,10 +6081,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515159</v>
+        <v>515039</v>
       </c>
       <c r="R47" t="n">
-        <v>6704968</v>
+        <v>6704836</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6121,6 +6117,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6147,7 +6148,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119650185</v>
+        <v>119650187</v>
       </c>
       <c r="B48" t="n">
         <v>91840</v>
@@ -6181,16 +6182,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515338</v>
+        <v>515163</v>
       </c>
       <c r="R48" t="n">
-        <v>6704861</v>
+        <v>6704951</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6227,7 +6231,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>7 fk. +gamla</t>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6236,6 +6240,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6254,7 +6259,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119650187</v>
+        <v>119650184</v>
       </c>
       <c r="B49" t="n">
         <v>91840</v>
@@ -6288,19 +6293,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515163</v>
+        <v>515345</v>
       </c>
       <c r="R49" t="n">
-        <v>6704951</v>
+        <v>6704830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6335,18 +6337,12 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>5 ex.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6472,10 +6468,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119650188</v>
+        <v>119650181</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6484,25 +6480,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6512,10 +6508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515039</v>
+        <v>515159</v>
       </c>
       <c r="R51" t="n">
-        <v>6704836</v>
+        <v>6704968</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6548,11 +6544,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6579,10 +6570,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119647895</v>
+        <v>119650185</v>
       </c>
       <c r="B52" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6591,50 +6582,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515364</v>
+        <v>515338</v>
       </c>
       <c r="R52" t="n">
-        <v>6704871</v>
+        <v>6704861</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6661,24 +6643,14 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ett 15-tal fk minst.</t>
+          <t>7 fk. +gamla</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6705,10 +6677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119650186</v>
+        <v>119647895</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6717,41 +6689,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515367</v>
+        <v>515364</v>
       </c>
       <c r="R53" t="n">
-        <v>6704895</v>
+        <v>6704871</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6778,14 +6759,24 @@
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>3 fk + gamla fk.</t>
+          <t>Ett 15-tal fk minst.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6812,10 +6803,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119650184</v>
+        <v>119650180</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6824,38 +6815,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515345</v>
+        <v>515044</v>
       </c>
       <c r="R54" t="n">
-        <v>6704830</v>
+        <v>6704840</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6890,12 +6884,18 @@
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Små tunn fot.??</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>121212113</v>
       </c>
       <c r="B55" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>121212113</v>
       </c>
       <c r="B55" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>121212113</v>
       </c>
       <c r="B55" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>121212113</v>
       </c>
       <c r="B55" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>121212113</v>
       </c>
       <c r="B55" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>121212113</v>
       </c>
       <c r="B55" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6998,6 +6998,337 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122978613</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91389</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sims, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>515226</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6704758</v>
+      </c>
+      <c r="S56" t="n">
+        <v>75</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122981082</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sims, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>515351</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6704716</v>
+      </c>
+      <c r="S57" t="n">
+        <v>75</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122978833</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sims, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>515243</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6704777</v>
+      </c>
+      <c r="S58" t="n">
+        <v>75</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7000,10 +7000,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122978613</v>
+        <v>122981082</v>
       </c>
       <c r="B56" t="n">
-        <v>91389</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7012,30 +7012,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7043,10 +7048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515226</v>
+        <v>515351</v>
       </c>
       <c r="R56" t="n">
-        <v>6704758</v>
+        <v>6704716</v>
       </c>
       <c r="S56" t="n">
         <v>75</v>
@@ -7081,13 +7086,17 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7106,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122981082</v>
+        <v>122978833</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7118,25 +7127,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7144,7 +7153,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7154,10 +7163,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515351</v>
+        <v>515243</v>
       </c>
       <c r="R57" t="n">
-        <v>6704716</v>
+        <v>6704777</v>
       </c>
       <c r="S57" t="n">
         <v>75</v>
@@ -7190,11 +7199,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7221,10 +7225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122978833</v>
+        <v>122978613</v>
       </c>
       <c r="B58" t="n">
-        <v>56688</v>
+        <v>91389</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7233,35 +7237,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7269,10 +7268,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515243</v>
+        <v>515226</v>
       </c>
       <c r="R58" t="n">
-        <v>6704777</v>
+        <v>6704758</v>
       </c>
       <c r="S58" t="n">
         <v>75</v>
@@ -7313,6 +7312,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7000,10 +7000,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122981082</v>
+        <v>122978833</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7012,25 +7012,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515351</v>
+        <v>515243</v>
       </c>
       <c r="R56" t="n">
-        <v>6704716</v>
+        <v>6704777</v>
       </c>
       <c r="S56" t="n">
         <v>75</v>
@@ -7084,11 +7084,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7115,10 +7110,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122978833</v>
+        <v>122981082</v>
       </c>
       <c r="B57" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7127,25 +7122,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7153,7 +7148,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7163,10 +7158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515243</v>
+        <v>515351</v>
       </c>
       <c r="R57" t="n">
-        <v>6704777</v>
+        <v>6704716</v>
       </c>
       <c r="S57" t="n">
         <v>75</v>
@@ -7199,6 +7194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7228,7 +7228,7 @@
         <v>122978613</v>
       </c>
       <c r="B58" t="n">
-        <v>91389</v>
+        <v>91397</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7000,10 +7000,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122978833</v>
+        <v>122981082</v>
       </c>
       <c r="B56" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7012,25 +7012,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515243</v>
+        <v>515351</v>
       </c>
       <c r="R56" t="n">
-        <v>6704777</v>
+        <v>6704716</v>
       </c>
       <c r="S56" t="n">
         <v>75</v>
@@ -7084,6 +7084,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7110,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122981082</v>
+        <v>122978613</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>91397</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7122,35 +7127,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515351</v>
+        <v>515226</v>
       </c>
       <c r="R57" t="n">
-        <v>6704716</v>
+        <v>6704758</v>
       </c>
       <c r="S57" t="n">
         <v>75</v>
@@ -7196,17 +7196,13 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7225,10 +7221,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122978613</v>
+        <v>122978833</v>
       </c>
       <c r="B58" t="n">
-        <v>91397</v>
+        <v>56688</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7237,30 +7233,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7268,10 +7269,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515226</v>
+        <v>515243</v>
       </c>
       <c r="R58" t="n">
-        <v>6704758</v>
+        <v>6704777</v>
       </c>
       <c r="S58" t="n">
         <v>75</v>
@@ -7312,7 +7313,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>66501238</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>66501260</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>122981082</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>122978613</v>
       </c>
       <c r="B57" t="n">
-        <v>91397</v>
+        <v>91400</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>122978833</v>
       </c>
       <c r="B58" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7115,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122978613</v>
+        <v>122978833</v>
       </c>
       <c r="B57" t="n">
-        <v>91400</v>
+        <v>56691</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7127,30 +7127,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7158,10 +7163,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515226</v>
+        <v>515243</v>
       </c>
       <c r="R57" t="n">
-        <v>6704758</v>
+        <v>6704777</v>
       </c>
       <c r="S57" t="n">
         <v>75</v>
@@ -7202,7 +7207,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7221,10 +7225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122978833</v>
+        <v>122978613</v>
       </c>
       <c r="B58" t="n">
-        <v>56691</v>
+        <v>91402</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7233,35 +7237,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7269,10 +7268,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515243</v>
+        <v>515226</v>
       </c>
       <c r="R58" t="n">
-        <v>6704777</v>
+        <v>6704758</v>
       </c>
       <c r="S58" t="n">
         <v>75</v>
@@ -7313,6 +7312,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7000,10 +7000,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122981082</v>
+        <v>122978833</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7012,25 +7012,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515351</v>
+        <v>515243</v>
       </c>
       <c r="R56" t="n">
-        <v>6704716</v>
+        <v>6704777</v>
       </c>
       <c r="S56" t="n">
         <v>75</v>
@@ -7084,11 +7084,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7115,10 +7110,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122978833</v>
+        <v>122981082</v>
       </c>
       <c r="B57" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7127,25 +7122,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7153,7 +7148,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7163,10 +7158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515243</v>
+        <v>515351</v>
       </c>
       <c r="R57" t="n">
-        <v>6704777</v>
+        <v>6704716</v>
       </c>
       <c r="S57" t="n">
         <v>75</v>
@@ -7199,6 +7194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7228,7 +7228,7 @@
         <v>122978613</v>
       </c>
       <c r="B58" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7000,10 +7000,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122978613</v>
+        <v>122981082</v>
       </c>
       <c r="B56" t="n">
-        <v>91411</v>
+        <v>57487</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7012,30 +7012,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7043,10 +7048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515226</v>
+        <v>515351</v>
       </c>
       <c r="R56" t="n">
-        <v>6704758</v>
+        <v>6704716</v>
       </c>
       <c r="S56" t="n">
         <v>75</v>
@@ -7081,13 +7086,17 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7106,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122978833</v>
+        <v>122978613</v>
       </c>
       <c r="B57" t="n">
-        <v>56691</v>
+        <v>91428</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7118,35 +7127,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7154,10 +7158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515243</v>
+        <v>515226</v>
       </c>
       <c r="R57" t="n">
-        <v>6704777</v>
+        <v>6704758</v>
       </c>
       <c r="S57" t="n">
         <v>75</v>
@@ -7198,6 +7202,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7216,10 +7221,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122981082</v>
+        <v>122978833</v>
       </c>
       <c r="B58" t="n">
-        <v>57481</v>
+        <v>56697</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7228,25 +7233,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7254,7 +7259,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7264,10 +7269,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515351</v>
+        <v>515243</v>
       </c>
       <c r="R58" t="n">
-        <v>6704716</v>
+        <v>6704777</v>
       </c>
       <c r="S58" t="n">
         <v>75</v>
@@ -7300,11 +7305,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7329,6 +7329,134 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123771772</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Simsbodarna Ö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>515374</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6704855</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7334,7 +7334,7 @@
         <v>123771772</v>
       </c>
       <c r="B59" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -3970,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7577,7 +7577,7 @@
         <v>131219164</v>
       </c>
       <c r="B61" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>131273902</v>
       </c>
       <c r="B62" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>131273875</v>
       </c>
       <c r="B63" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>131273771</v>
       </c>
       <c r="B64" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7577,7 +7577,7 @@
         <v>131219164</v>
       </c>
       <c r="B61" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>131273902</v>
       </c>
       <c r="B62" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>131273875</v>
       </c>
       <c r="B63" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>131273771</v>
       </c>
       <c r="B64" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -7687,7 +7687,7 @@
         <v>131273902</v>
       </c>
       <c r="B62" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>131273875</v>
       </c>
       <c r="B63" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>131273771</v>
       </c>
       <c r="B64" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8007,6 +8007,125 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>85911704</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57991</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>515007</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6704927</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2020-05-30</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2020-05-30</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo Johansson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo Johansson, Solgerd Skoog Johansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56153834</v>
+        <v>71197672</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,17 +708,17 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515187.4365601228</v>
+        <v>515741</v>
       </c>
       <c r="R2" t="n">
-        <v>6704935.632626219</v>
+        <v>6704313</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +742,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt på en granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,70 +783,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Sören Nyström</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56153815</v>
+        <v>66501253</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515046.6081341765</v>
+        <v>515262</v>
       </c>
       <c r="R3" t="n">
-        <v>6704840.88442698</v>
+        <v>6704842</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,34 +869,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>14063</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Sören Nyström</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66501240</v>
+        <v>71197632</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,37 +903,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515409.0882672406</v>
+        <v>515557</v>
       </c>
       <c r="R4" t="n">
-        <v>6704717.18770413</v>
+        <v>6704782</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,76 +983,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>14051</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66501237</v>
+        <v>121212113</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Sims bodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515253.4515458706</v>
+        <v>515239</v>
       </c>
       <c r="R5" t="n">
-        <v>6704854.567987938</v>
+        <v>6704955</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,76 +1084,70 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>14049</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66501259</v>
+        <v>122978613</v>
       </c>
       <c r="B6" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Sims, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515398.3566778041</v>
+        <v>515226</v>
       </c>
       <c r="R6" t="n">
-        <v>6704686.082408887</v>
+        <v>6704758</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,22 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,42 +1185,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>14069</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66501258</v>
+        <v>56153815</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1296,20 +1232,30 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515398.3566778041</v>
+        <v>515047</v>
       </c>
       <c r="R7" t="n">
-        <v>6704686.082408887</v>
+        <v>6704841</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,38 +1293,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>14068</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson, Sören Nyström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66501238</v>
+        <v>66501237</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515409</v>
+        <v>515253</v>
       </c>
       <c r="R8" t="n">
-        <v>6704717</v>
+        <v>6704855</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1458,11 +1385,6 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>bohål</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1474,7 +1396,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1492,19 +1414,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66501250</v>
+        <v>66501249</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1532,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515443.0835266049</v>
+        <v>515244</v>
       </c>
       <c r="R9" t="n">
-        <v>6704619.715729647</v>
+        <v>6704932</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1565,26 +1482,11 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1596,7 +1498,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1614,19 +1516,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66501249</v>
+        <v>66501250</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1654,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515243.741529665</v>
+        <v>515443</v>
       </c>
       <c r="R10" t="n">
-        <v>6704932.41849437</v>
+        <v>6704620</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1687,19 +1584,14 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1605,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1731,15 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66501246</v>
+        <v>66501258</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,38 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515132.7634908516</v>
+        <v>515398</v>
       </c>
       <c r="R11" t="n">
-        <v>6704902.86692916</v>
+        <v>6704686</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1808,21 +1691,11 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1834,7 +1707,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1852,15 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66501254</v>
+        <v>73040174</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,37 +1736,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515725.4234272207</v>
+        <v>515347</v>
       </c>
       <c r="R12" t="n">
-        <v>6704422.238333618</v>
+        <v>6704754</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,22 +1796,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>G:a fk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,38 +1815,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>14064</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66501253</v>
+        <v>97182345</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,37 +1845,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515262.3937595382</v>
+        <v>515071</v>
       </c>
       <c r="R13" t="n">
-        <v>6704841.787950627</v>
+        <v>6704588</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,22 +1909,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,36 +1935,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>14063</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66501295</v>
+        <v>97183373</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,41 +1962,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515157.1366205646</v>
+        <v>515300</v>
       </c>
       <c r="R14" t="n">
-        <v>6704978.394420556</v>
+        <v>6704658</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2160,62 +2021,52 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>14102</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66501260</v>
+        <v>97183484</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,37 +2074,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515398</v>
+        <v>515471</v>
       </c>
       <c r="R15" t="n">
-        <v>6704686</v>
+        <v>6704825</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2277,12 +2138,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,36 +2164,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>14070</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66501248</v>
+        <v>97183618</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2330,41 +2191,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515191.4447045195</v>
+        <v>515515</v>
       </c>
       <c r="R16" t="n">
-        <v>6704921.846042051</v>
+        <v>6704824</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,22 +2255,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,36 +2281,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>14058</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>70273918</v>
+        <v>97184504</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,39 +2308,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515114.975050035</v>
+        <v>515536</v>
       </c>
       <c r="R17" t="n">
-        <v>6704905.750487493</v>
+        <v>6704802</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,22 +2372,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-03-31</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-03-31</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 kvm.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2549,15 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>70273904</v>
+        <v>97188740</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,36 +2430,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515217.8528258898</v>
+        <v>515572</v>
       </c>
       <c r="R18" t="n">
-        <v>6704747.930965496</v>
+        <v>6704791</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2621,22 +2495,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-03-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-03-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,6 +2509,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2663,15 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>73040286</v>
+        <v>100761459</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,39 +2539,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515172.0571806447</v>
+        <v>515596</v>
       </c>
       <c r="R19" t="n">
-        <v>6704952.822304476</v>
+        <v>6704393</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2735,22 +2603,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fjolårets fk.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2759,7 +2632,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2778,15 +2650,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73040254</v>
+        <v>100762584</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,39 +2661,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515267.2089520991</v>
+        <v>515759</v>
       </c>
       <c r="R20" t="n">
-        <v>6704870.894593589</v>
+        <v>6704420</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2850,22 +2725,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjolårets.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,7 +2754,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2893,19 +2772,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>73040174</v>
+        <v>112210968</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2939,13 +2813,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515347.2057839864</v>
+        <v>514995</v>
       </c>
       <c r="R21" t="n">
-        <v>6704753.900175091</v>
+        <v>6704848</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,22 +2843,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2998,7 +2872,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3017,15 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>73040278</v>
+        <v>112211016</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,25 +2901,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3059,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515178.0406731129</v>
+        <v>515070</v>
       </c>
       <c r="R22" t="n">
-        <v>6704821.220549313</v>
+        <v>6704835</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3089,22 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,7 +2989,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3132,15 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>92434398</v>
+        <v>112211929</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,45 +3018,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>SO Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515599.2161575644</v>
+        <v>515369</v>
       </c>
       <c r="R23" t="n">
-        <v>6704715.044077382</v>
+        <v>6704610</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3213,27 +3082,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På äldre tall.</t>
+          <t>G:a fk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,7 +3111,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3261,15 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>92434489</v>
+        <v>112212094</v>
       </c>
       <c r="B24" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3277,26 +3140,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3305,20 +3168,19 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>SO Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515580.9410935603</v>
+        <v>515450</v>
       </c>
       <c r="R24" t="n">
-        <v>6704715.95137801</v>
+        <v>6704585</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3342,22 +3204,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca. Färska fk.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,7 +3233,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3385,15 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97182860</v>
+        <v>112212309</v>
       </c>
       <c r="B25" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,26 +3262,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3431,17 +3292,17 @@
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515190.1633922675</v>
+        <v>515492</v>
       </c>
       <c r="R25" t="n">
-        <v>6704638.859276415</v>
+        <v>6704592</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3465,22 +3326,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3507,19 +3368,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97182345</v>
+        <v>112212369</v>
       </c>
       <c r="B26" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3542,7 +3398,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3553,14 +3409,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515070.8733393272</v>
+        <v>515497</v>
       </c>
       <c r="R26" t="n">
-        <v>6704587.086380764</v>
+        <v>6704555</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -3587,22 +3443,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,15 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97183367</v>
+        <v>112212788</v>
       </c>
       <c r="B27" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3645,26 +3496,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3675,17 +3526,17 @@
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515299.7114049749</v>
+        <v>515101</v>
       </c>
       <c r="R27" t="n">
-        <v>6704658.05531624</v>
+        <v>6704642</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3709,22 +3560,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3751,19 +3602,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97183484</v>
+        <v>112274081</v>
       </c>
       <c r="B28" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3786,7 +3632,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3795,19 +3641,20 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna Ö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515470.8483822512</v>
+        <v>515374</v>
       </c>
       <c r="R28" t="n">
-        <v>6704824.92528184</v>
+        <v>6704855</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3831,22 +3678,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,37 +3702,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97183373</v>
+        <v>112274505</v>
       </c>
       <c r="B29" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3908,23 +3751,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna Ö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515299.7114049749</v>
+        <v>515431</v>
       </c>
       <c r="R29" t="n">
-        <v>6704658.05531624</v>
+        <v>6704883</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3948,57 +3797,53 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97568830</v>
+        <v>112536735</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4006,38 +3851,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515128.8420988508</v>
+        <v>515320</v>
       </c>
       <c r="R30" t="n">
-        <v>6704895.948777406</v>
+        <v>6704905</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,22 +3906,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4091,31 +3926,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>100762584</v>
+        <v>119650183</v>
       </c>
       <c r="B31" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4136,30 +3966,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515758.5218339698</v>
+        <v>515007</v>
       </c>
       <c r="R31" t="n">
-        <v>6704419.917029182</v>
+        <v>6704835</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4183,27 +4003,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fjolårets.</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4212,6 +4022,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4230,19 +4041,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112211016</v>
+        <v>119650184</v>
       </c>
       <c r="B32" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4263,30 +4069,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515070</v>
+        <v>515345</v>
       </c>
       <c r="R32" t="n">
-        <v>6704834</v>
+        <v>6704830</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4310,22 +4106,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4352,19 +4138,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112211929</v>
+        <v>119650185</v>
       </c>
       <c r="B33" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4385,30 +4166,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>SO Simsbodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515370</v>
+        <v>515338</v>
       </c>
       <c r="R33" t="n">
-        <v>6704610</v>
+        <v>6704861</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4432,27 +4203,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>G:a fk.</t>
+          <t>7 fk. +gamla</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4479,15 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112211876</v>
+        <v>119650186</v>
       </c>
       <c r="B34" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4495,47 +4251,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>SO Simsbodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>515371</v>
+        <v>515367</v>
       </c>
       <c r="R34" t="n">
-        <v>6704633</v>
+        <v>6704895</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4559,22 +4305,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 fk + gamla fk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4601,19 +4342,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112212369</v>
+        <v>119650187</v>
       </c>
       <c r="B35" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4634,30 +4370,23 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>515497</v>
+        <v>515163</v>
       </c>
       <c r="R35" t="n">
-        <v>6704555</v>
+        <v>6704951</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4681,22 +4410,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4705,6 +4429,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4723,19 +4448,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112212788</v>
+        <v>119650188</v>
       </c>
       <c r="B36" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4756,30 +4476,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515101</v>
+        <v>515039</v>
       </c>
       <c r="R36" t="n">
-        <v>6704641</v>
+        <v>6704836</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4803,22 +4513,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>5 ex.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4845,42 +4550,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112212309</v>
+        <v>92434489</v>
       </c>
       <c r="B37" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4889,19 +4589,20 @@
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>SO Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515492</v>
+        <v>515581</v>
       </c>
       <c r="R37" t="n">
-        <v>6704591</v>
+        <v>6704716</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,22 +4626,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4949,6 +4650,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4967,63 +4669,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112212237</v>
+        <v>71197708</v>
       </c>
       <c r="B38" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515492</v>
+        <v>515604</v>
       </c>
       <c r="R38" t="n">
-        <v>6704591</v>
+        <v>6704760</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5047,27 +4736,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Stora fina ex.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5076,6 +4760,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5094,15 +4779,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112212094</v>
+        <v>112211348</v>
       </c>
       <c r="B39" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5110,47 +4790,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515450</v>
+        <v>515174</v>
       </c>
       <c r="R39" t="n">
-        <v>6704585</v>
+        <v>6704768</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5179,7 +4850,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5189,12 +4860,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ca. Färska fk.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5221,15 +4887,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112212286</v>
+        <v>119650180</v>
       </c>
       <c r="B40" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5237,47 +4898,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515476</v>
+        <v>515044</v>
       </c>
       <c r="R40" t="n">
-        <v>6704606</v>
+        <v>6704840</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5301,30 +4955,26 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Små tunn fot.??</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5343,40 +4993,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112211348</v>
+        <v>97182860</v>
       </c>
       <c r="B41" t="n">
-        <v>89556</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5384,13 +5038,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515173</v>
+        <v>515190</v>
       </c>
       <c r="R41" t="n">
-        <v>6704768</v>
+        <v>6704638</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5414,22 +5068,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5456,15 +5110,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112274101</v>
+        <v>97183367</v>
       </c>
       <c r="B42" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,23 +5138,30 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Simsbodarna SÖ, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515488</v>
+        <v>515300</v>
       </c>
       <c r="R42" t="n">
-        <v>6704599</v>
+        <v>6704658</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5529,27 +5185,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5558,61 +5209,55 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112274081</v>
+        <v>112211876</v>
       </c>
       <c r="B43" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5621,20 +5266,19 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Simsbodarna Ö, Dlr</t>
+          <t>SO Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515374</v>
+        <v>515371</v>
       </c>
       <c r="R43" t="n">
-        <v>6704855</v>
+        <v>6704633</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5658,22 +5302,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5682,73 +5326,76 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112536735</v>
+        <v>112212237</v>
       </c>
       <c r="B44" t="n">
-        <v>91161</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Simsbodarna (Simsbodarna), Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515321</v>
+        <v>515492</v>
       </c>
       <c r="R44" t="n">
-        <v>6704905</v>
+        <v>6704592</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5772,12 +5419,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Stora fina ex.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5792,73 +5454,70 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117178692</v>
+        <v>112212286</v>
       </c>
       <c r="B45" t="n">
-        <v>56496</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515348</v>
+        <v>515476</v>
       </c>
       <c r="R45" t="n">
-        <v>6704885</v>
+        <v>6704607</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5882,12 +5541,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5902,65 +5571,63 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119650186</v>
+        <v>112274101</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SÖ, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515367</v>
+        <v>515487</v>
       </c>
       <c r="R46" t="n">
-        <v>6704895</v>
+        <v>6704599</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5984,17 +5651,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>3 fk + gamla fk.</t>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,68 +5680,66 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119650188</v>
+        <v>56153834</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515039</v>
+        <v>515187</v>
       </c>
       <c r="R47" t="n">
-        <v>6704836</v>
+        <v>6704936</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6091,17 +5766,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>5 ex.</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6121,63 +5791,55 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Sören Nyström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119650187</v>
+        <v>66501240</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515163</v>
+        <v>515409</v>
       </c>
       <c r="R48" t="n">
-        <v>6704951</v>
+        <v>6704717</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6201,17 +5863,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>5 ex.</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6220,72 +5877,75 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>14051</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119650184</v>
+        <v>66501246</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>515345</v>
+        <v>515133</v>
       </c>
       <c r="R49" t="n">
-        <v>6704830</v>
+        <v>6704903</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6309,12 +5969,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,69 +5985,73 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>14057</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119650182</v>
+        <v>66501248</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>515134</v>
+        <v>515191</v>
       </c>
       <c r="R50" t="n">
-        <v>6704882</v>
+        <v>6704922</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6411,17 +6075,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Sammanvuxna till två större fk.</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6432,69 +6091,73 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>14058</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119650181</v>
+        <v>66501295</v>
       </c>
       <c r="B51" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>515159</v>
+        <v>515157</v>
       </c>
       <c r="R51" t="n">
-        <v>6704968</v>
+        <v>6704978</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6518,12 +6181,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,69 +6197,71 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119650185</v>
+        <v>70273904</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>515338</v>
+        <v>515218</v>
       </c>
       <c r="R52" t="n">
-        <v>6704861</v>
+        <v>6704748</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6620,17 +6285,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2018-03-31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>7 fk. +gamla</t>
+          <t>2018-03-31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6657,62 +6317,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119647895</v>
+        <v>70273918</v>
       </c>
       <c r="B53" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>515364</v>
+        <v>515115</v>
       </c>
       <c r="R53" t="n">
-        <v>6704871</v>
+        <v>6704906</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6736,27 +6384,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2018-03-31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ett 15-tal fk minst.</t>
+          <t>2018-03-31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6783,56 +6416,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119650180</v>
+        <v>73040254</v>
       </c>
       <c r="B54" t="n">
-        <v>91883</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>515044</v>
+        <v>515267</v>
       </c>
       <c r="R54" t="n">
-        <v>6704840</v>
+        <v>6704871</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6856,24 +6483,19 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Små tunn fot.??</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
@@ -6894,56 +6516,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212113</v>
+        <v>73040278</v>
       </c>
       <c r="B55" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sims bodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515239</v>
+        <v>515178</v>
       </c>
       <c r="R55" t="n">
-        <v>6704955</v>
+        <v>6704821</v>
       </c>
       <c r="S55" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6967,12 +6583,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6988,73 +6604,62 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122981082</v>
+        <v>73040286</v>
       </c>
       <c r="B56" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sims, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515351</v>
+        <v>515172</v>
       </c>
       <c r="R56" t="n">
-        <v>6704716</v>
+        <v>6704953</v>
       </c>
       <c r="S56" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7078,17 +6683,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7097,33 +6697,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122978613</v>
+        <v>92434398</v>
       </c>
       <c r="B57" t="n">
-        <v>91428</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7131,40 +6727,48 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sims, Dlr</t>
+          <t>SO Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515226</v>
+        <v>515599</v>
       </c>
       <c r="R57" t="n">
-        <v>6704758</v>
+        <v>6704715</v>
       </c>
       <c r="S57" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7188,12 +6792,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7209,73 +6828,61 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122978833</v>
+        <v>97568830</v>
       </c>
       <c r="B58" t="n">
-        <v>56697</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sims, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>515243</v>
+        <v>515129</v>
       </c>
       <c r="R58" t="n">
-        <v>6704777</v>
+        <v>6704895</v>
       </c>
       <c r="S58" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7299,12 +6906,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7319,81 +6936,61 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123771772</v>
+        <v>112536226</v>
       </c>
       <c r="B59" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Simsbodarna Ö, Dlr</t>
+          <t>Simsbodarna, Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>515374</v>
+        <v>515115</v>
       </c>
       <c r="R59" t="n">
-        <v>6704855</v>
+        <v>6704978</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7417,22 +7014,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>08:40</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7447,70 +7034,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124556699</v>
+        <v>66501259</v>
       </c>
       <c r="B60" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sims, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>515213</v>
+        <v>515398</v>
       </c>
       <c r="R60" t="n">
-        <v>6704893</v>
+        <v>6704686</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7537,17 +7111,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7558,26 +7127,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>14069</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131219164</v>
+        <v>66501238</v>
       </c>
       <c r="B61" t="n">
-        <v>57899</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7603,24 +7177,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sims bodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>515143</v>
+        <v>515409</v>
       </c>
       <c r="R61" t="n">
-        <v>6704966</v>
+        <v>6704717</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7647,17 +7213,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>bohål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7668,26 +7234,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>14050</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131273902</v>
+        <v>66501260</v>
       </c>
       <c r="B62" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7713,24 +7284,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sims fäbodar, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>515081</v>
+        <v>515398</v>
       </c>
       <c r="R62" t="n">
-        <v>6704854</v>
+        <v>6704686</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7757,17 +7320,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7778,26 +7336,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>14070</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131273875</v>
+        <v>71197550</v>
       </c>
       <c r="B63" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7827,23 +7390,22 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sims fäbodar, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>515025</v>
+        <v>515556</v>
       </c>
       <c r="R63" t="n">
-        <v>6704768</v>
+        <v>6704791</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7867,17 +7429,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2018-05-09</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2018-05-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Hackringar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7892,44 +7464,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131273771</v>
+        <v>122981082</v>
       </c>
       <c r="B64" t="n">
-        <v>57090</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7937,23 +7509,23 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sims fäbodar, Dlr</t>
+          <t>Sims, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>515338</v>
+        <v>515351</v>
       </c>
       <c r="R64" t="n">
-        <v>6704939</v>
+        <v>6704716</v>
       </c>
       <c r="S64" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7977,12 +7549,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8009,60 +7586,56 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>85911704</v>
+        <v>124556699</v>
       </c>
       <c r="B65" t="n">
-        <v>58039</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102626</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Borlänge, Dlr</t>
+          <t>Sims, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>515007</v>
+        <v>515213</v>
       </c>
       <c r="R65" t="n">
-        <v>6704927</v>
+        <v>6704893</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8086,22 +7659,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2020-05-30</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>19:15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2020-05-30</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>19:15</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8116,15 +7684,1851 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131219164</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sims bodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>515143</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6704966</v>
+      </c>
+      <c r="S66" t="n">
+        <v>50</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131273875</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sims fäbodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>515025</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6704768</v>
+      </c>
+      <c r="S67" t="n">
+        <v>50</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131273902</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sims fäbodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>515081</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6704854</v>
+      </c>
+      <c r="S68" t="n">
+        <v>50</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>70273853</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Simsbodarna S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>515438</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6704667</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>97183364</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Simsbodarna S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>515281</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6704650</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På marken. Bärris, ljung.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>97183561</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Simsbodarna SO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>515502</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6704824</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2021-11-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>I tall.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>97304695</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SO Simsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>515358</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6704803</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>I tall.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>100760050</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Simsbodarna SO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>515476</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6704607</v>
+      </c>
+      <c r="S73" t="n">
+        <v>6</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>100760825</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Simsbodarna SO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>515595</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6704552</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>100763119</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Simsbodarna SO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>515653</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6704652</v>
+      </c>
+      <c r="S75" t="n">
+        <v>8</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2022-05-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Möjlig spelplats för enstaka tupp.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>107216033</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Simsbodarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>515508</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6704789</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>117178692</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Simsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>515348</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6704885</v>
+      </c>
+      <c r="S77" t="n">
+        <v>75</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122978833</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sims, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>515243</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6704777</v>
+      </c>
+      <c r="S78" t="n">
+        <v>75</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123771772</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Simsbodarna Ö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>515374</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6704855</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Håkan Sandin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131273771</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sims fäbodar, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>515338</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6704939</v>
+      </c>
+      <c r="S80" t="n">
+        <v>50</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>85911704</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>515007</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6704927</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2020-05-30</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2020-05-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
           <t>Bo Johansson</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AX81" t="inlineStr">
         <is>
           <t>Bo Johansson, Solgerd Skoog Johansson</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73613-2021 artfynd.xlsx
+++ b/artfynd/A 73613-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501253</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197632</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122978613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56153815</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501237</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501249</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501250</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501258</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97182345</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183484</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183618</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2416,6 +2496,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97184504</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2525,6 +2610,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97188740</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100761459</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2769,6 +2864,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100762584</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112210968</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3004,6 +3109,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211016</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3126,6 +3236,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211929</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3248,6 +3363,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212094</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3365,6 +3485,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212309</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3482,6 +3607,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212369</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3599,6 +3729,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212788</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3718,6 +3853,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112274081</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3837,6 +3977,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112274505</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3935,6 +4080,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112536735</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4038,6 +4188,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650183</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4135,6 +4290,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650184</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4237,6 +4397,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650185</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4339,6 +4504,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650186</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4445,6 +4615,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650187</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4547,6 +4722,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650188</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4666,6 +4846,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92434489</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4776,6 +4961,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197708</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4884,6 +5074,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211348</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4990,6 +5185,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650180</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5107,6 +5307,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97182860</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5224,6 +5429,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183367</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5341,6 +5551,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211876</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5463,6 +5678,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212237</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5580,6 +5800,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212286</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5696,6 +5921,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112274101</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5795,6 +6025,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56153834</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5897,6 +6132,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501240</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6003,6 +6243,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501246</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6109,6 +6354,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501248</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6215,6 +6465,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501295</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6314,6 +6569,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70273904</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6413,6 +6673,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70273918</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6513,6 +6778,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040254</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6613,6 +6883,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040278</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6713,6 +6988,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040286</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6837,6 +7117,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92434398</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6945,6 +7230,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97568830</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7043,6 +7333,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112536226</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7145,6 +7440,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501259</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7252,6 +7552,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501238</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7354,6 +7659,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501260</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7473,6 +7783,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197550</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7583,6 +7898,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122981082</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7693,6 +8013,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124556699</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7803,6 +8128,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131219164</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7913,6 +8243,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131273875</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8023,6 +8358,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131273902</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8127,6 +8467,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70273853</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8258,6 +8603,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183364</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8389,6 +8739,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183561</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8507,6 +8862,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97304695</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8621,6 +8981,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100760050</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8735,6 +9100,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100760825</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8854,6 +9224,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100763119</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8972,6 +9347,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107216033</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9077,6 +9457,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117178692</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9182,6 +9567,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122978833</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9305,6 +9695,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771772</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9410,6 +9805,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131273771</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9529,8 +9929,95 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85911704</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>